--- a/init-ig/ig/all-profiles.xlsx
+++ b/init-ig/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T08:51:21+00:00</t>
+    <t>2026-09-28T08:56:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
